--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488018_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488018_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. PEREZ GARCIA</t>
+          <t>H. TAVIO SOLIS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6402</v>
+        <v>2.4792</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7716</v>
+        <v>1.6499</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1314</v>
+        <v>0.8293</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0251</v>
+        <v>1.902</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6029</v>
+        <v>0.1801</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5778</v>
+        <v>1.7219</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6778</v>
+        <v>1.6168</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4691</v>
+        <v>0.4439</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2087</v>
+        <v>1.1729</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.6527</v>
+        <v>0.2852</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8662</v>
+        <v>-0.2638</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7864</v>
+        <v>0.549</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.3698</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9733</v>
+        <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3417</v>
+        <v>-0.4231</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7937</v>
+        <v>0.0331</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4521</v>
+        <v>-0.4562</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6698</v>
+        <v>-0.3873</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6698</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.3873</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. WRIGHT RODRIGUEZ</t>
+          <t>A. PEREZ GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4881</v>
+        <v>2.3897</v>
       </c>
       <c r="E3" t="n">
-        <v>3.792</v>
+        <v>2.5492</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3039</v>
+        <v>-0.1595</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1818</v>
+        <v>0.0251</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5128</v>
+        <v>0.6029</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.331</v>
+        <v>-0.5778</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5165</v>
+        <v>2.6778</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1103</v>
+        <v>2.4691</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4062</v>
+        <v>0.2087</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3347</v>
+        <v>-2.6527</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5975</v>
+        <v>-1.8662</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7372</v>
+        <v>-0.7864</v>
       </c>
       <c r="P3" t="n">
-        <v>1.784</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1982</v>
+        <v>-3.3698</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9822</v>
+        <v>2.9733</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0554</v>
+        <v>1.0912</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8701</v>
+        <v>1.5713</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1853</v>
+        <v>-0.4801</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5331</v>
+        <v>1.6698</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6036</v>
+        <v>1.6698</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>D. WRIGHT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4813</v>
+        <v>2.0026</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6929</v>
+        <v>3.4469</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2115</v>
+        <v>-1.4443</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6868</v>
+        <v>0.1818</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2028</v>
+        <v>0.5128</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4839</v>
+        <v>-0.331</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6115</v>
+        <v>2.5165</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4106</v>
+        <v>1.1103</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2009</v>
+        <v>1.4062</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9247</v>
+        <v>-2.3347</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2078</v>
+        <v>-0.5975</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2831</v>
+        <v>-1.7372</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1627</v>
+        <v>-0.1982</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6904</v>
+        <v>0.5699</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2373</v>
+        <v>0.525</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4532</v>
+        <v>0.0449</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0864</v>
+        <v>-0.5331</v>
       </c>
       <c r="W4" t="n">
-        <v>2.0068</v>
+        <v>0.6036</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9204</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. TAVIO SOLIS</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.869</v>
+        <v>1.9188</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1801</v>
+        <v>2.5515</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6889</v>
+        <v>-0.6327</v>
       </c>
       <c r="G5" t="n">
-        <v>1.902</v>
+        <v>1.6868</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1801</v>
+        <v>1.2028</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7219</v>
+        <v>0.4839</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6168</v>
+        <v>3.6115</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4439</v>
+        <v>3.4106</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1729</v>
+        <v>0.2009</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2852</v>
+        <v>-1.9247</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2638</v>
+        <v>-2.2078</v>
       </c>
       <c r="O5" t="n">
-        <v>0.549</v>
+        <v>0.2831</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3876</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-4.1627</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876</v>
+        <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0333</v>
+        <v>1.1279</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4368</v>
+        <v>1.0959</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5966</v>
+        <v>0.032</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3873</v>
+        <v>1.0864</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.0068</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3873</v>
+        <v>-0.9204</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1601</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6929999999999999</v>
+        <v>1.9778</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.853</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>1.1396</v>
@@ -922,13 +922,13 @@
         <v>2.7751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8351</v>
+        <v>0.3093</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7891</v>
+        <v>0.4957</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.046</v>
+        <v>-0.1864</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2574</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5165</v>
+        <v>-1.7379</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3931</v>
+        <v>-0.6987</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1234</v>
+        <v>-1.0392</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1482</v>
@@ -1000,13 +1000,13 @@
         <v>1.9822</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7684</v>
+        <v>0.547</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8077</v>
+        <v>0.5021</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0393</v>
+        <v>0.0449</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1367</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. LOPEZ TORRE</t>
+          <t>M. VIGO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5799</v>
+        <v>-2.2541</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7879</v>
+        <v>-0.1234</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7919</v>
+        <v>-2.1307</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5341</v>
+        <v>-1.3783</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2274</v>
+        <v>-3.3164</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3067</v>
+        <v>1.9381</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5986</v>
+        <v>1.8779</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0404</v>
+        <v>-1.3842</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.639</v>
+        <v>3.2622</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9355</v>
+        <v>-3.2562</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2677</v>
+        <v>-1.9322</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6677</v>
+        <v>-1.3241</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9911</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1893</v>
+        <v>-3.3698</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1982</v>
+        <v>2.7751</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0547</v>
+        <v>0.3928</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.8353</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0547</v>
+        <v>-0.4425</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. VIGO RODRIGUEZ</t>
+          <t>G. LOPEZ TORRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.851</v>
+        <v>-2.3481</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3272</v>
+        <v>-1.5842</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5238</v>
+        <v>-0.7639</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3783</v>
+        <v>-1.5341</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.3164</v>
+        <v>-0.2274</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9381</v>
+        <v>-1.3067</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8779</v>
+        <v>-0.5986</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3842</v>
+        <v>0.0404</v>
       </c>
       <c r="L9" t="n">
-        <v>3.2622</v>
+        <v>-0.639</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.2562</v>
+        <v>-0.9355</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9322</v>
+        <v>-0.2677</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3241</v>
+        <v>-0.6677</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5947</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.3698</v>
+        <v>-1.1893</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7751</v>
+        <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.204</v>
+        <v>0.1771</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.2037</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8356</v>
+        <v>-0.0266</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0252</v>
+        <v>-3.4503</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3924</v>
+        <v>2.883</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.4176</v>
+        <v>-6.3333</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2409</v>
@@ -1234,13 +1234,13 @@
         <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9666</v>
+        <v>0.5415</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3621</v>
+        <v>0.8527</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3954</v>
+        <v>-0.3112</v>
       </c>
       <c r="V10" t="n">
         <v>-3.742</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2286</v>
+        <v>-4.555</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7199</v>
+        <v>-2.0463</v>
       </c>
       <c r="F11" t="n">
         <v>-2.5087</v>
@@ -1312,10 +1312,10 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1982</v>
+        <v>0.4754</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4368</v>
+        <v>0.2368</v>
       </c>
       <c r="U11" t="n">
         <v>0.2386</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.882699999999999</v>
+        <v>-4.570699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>10.2939</v>
+        <v>10.6057</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.1763</v>
+        <v>-15.1764</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8111</v>
@@ -1381,7 +1381,7 @@
         <v>-7.2708</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0001000000000001</v>
+        <v>0.000100000000000211</v>
       </c>
       <c r="Q12" t="n">
         <v>-18.8311</v>
@@ -1390,10 +1390,10 @@
         <v>18.8311</v>
       </c>
       <c r="S12" t="n">
-        <v>4.497199999999999</v>
+        <v>4.808999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>6.0398</v>
+        <v>6.3516</v>
       </c>
       <c r="U12" t="n">
         <v>-1.5426</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.738</v>
+        <v>12.7746</v>
       </c>
       <c r="E13" t="n">
-        <v>13.201</v>
+        <v>13.3029</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.463</v>
+        <v>-0.5283</v>
       </c>
       <c r="G13" t="n">
         <v>6.8816</v>
@@ -1468,13 +1468,13 @@
         <v>3.568</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7351</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.11</v>
+        <v>-0.0081</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.727</v>
       </c>
       <c r="V13" t="n">
         <v>6.2317</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>J. LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.489</v>
+        <v>2.0906</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6373</v>
+        <v>3.5081</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1484</v>
+        <v>-1.4176</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4259</v>
+        <v>1.9607</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9119</v>
+        <v>2.7318</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.486</v>
+        <v>-0.7712</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2779</v>
+        <v>4.3927</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2377</v>
+        <v>2.9061</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0402</v>
+        <v>1.4866</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.852</v>
+        <v>-2.432</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3258</v>
+        <v>-0.1743</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5262</v>
+        <v>-2.2577</v>
       </c>
       <c r="P14" t="n">
+        <v>1.9822</v>
+      </c>
+      <c r="Q14" t="n">
         <v>-1.1893</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-2.3787</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.1893</v>
+        <v>3.1716</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5716</v>
+        <v>-1.1784</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0573</v>
+        <v>-0.2284</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4857</v>
+        <v>-0.95</v>
       </c>
       <c r="V14" t="n">
-        <v>2.6808</v>
+        <v>-0.674</v>
       </c>
       <c r="W14" t="n">
-        <v>2.6808</v>
+        <v>0.5331</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUÑOZ</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5107</v>
+        <v>2.0743</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5107</v>
+        <v>2.0261</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.0482</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5107</v>
+        <v>0.4259</v>
       </c>
       <c r="H15" t="n">
-        <v>0.908</v>
+        <v>0.9119</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6027</v>
+        <v>-0.486</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5107</v>
+        <v>1.2779</v>
       </c>
       <c r="K15" t="n">
-        <v>0.908</v>
+        <v>1.2377</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6027</v>
+        <v>0.0402</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0.852</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.3258</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0.5262</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.3787</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.1569</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.4461</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0.2891</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUNOZ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.113</v>
+        <v>1.7</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9988</v>
+        <v>0.4001</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8858</v>
+        <v>1.2999</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9607</v>
+        <v>-1.5443</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7318</v>
+        <v>0.9734</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7712</v>
+        <v>-2.5177</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3927</v>
+        <v>0.2995</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9061</v>
+        <v>1.4931</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4866</v>
+        <v>-1.1937</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.432</v>
+        <v>-1.8438</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1743</v>
+        <v>-0.5198</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2577</v>
+        <v>-1.3241</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9822</v>
+        <v>2.5769</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1716</v>
+        <v>2.7751</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1559</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7377</v>
+        <v>0.0322</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4182</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.674</v>
+        <v>1.6145</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5331</v>
+        <v>0.2666</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2071</v>
+        <v>1.3479</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>J. LOPEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6101</v>
+        <v>1.5107</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1093</v>
+        <v>1.5107</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7194</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5443</v>
+        <v>1.5107</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9734</v>
+        <v>0.908</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5177</v>
+        <v>0.6027</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2995</v>
+        <v>1.5107</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4931</v>
+        <v>0.908</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1937</v>
+        <v>0.6027</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8438</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5198</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3241</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5769</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7751</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0369</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4771</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5598</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6145</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.3479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4888</v>
+        <v>0.0468</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5112</v>
+        <v>0.0468</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7482</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9779</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2297</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0526</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6866</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.366</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3044</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2913</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5957</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7751</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0345</v>
+        <v>0.0468</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9046999999999999</v>
+        <v>0.0468</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.0772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0187</v>
+        <v>0.0369</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1.3888</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0187</v>
+        <v>-1.3519</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.7482</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.9779</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.2297</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2.0526</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.6866</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.366</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.3044</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.2913</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.5957</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.7751</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0187</v>
+        <v>-0.4864</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.2589</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0187</v>
+        <v>-0.7453</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0494</v>
+        <v>-0.8842</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5</v>
+        <v>-0.1944</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5494</v>
+        <v>-0.6898</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2458</v>
@@ -2014,13 +2014,13 @@
         <v>0.5947</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2001</v>
+        <v>-0.0349</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2496</v>
+        <v>0.056</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0495</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GARCIA TEJON</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5386</v>
+        <v>-1.2551</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.978</v>
+        <v>0.5999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5606</v>
+        <v>-1.855</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5122</v>
+        <v>0.973</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4031</v>
+        <v>2.1211</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1091</v>
+        <v>-1.148</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1451</v>
+        <v>3.4807</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5379</v>
+        <v>2.6369</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.8437</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6574</v>
+        <v>-2.5076</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8652</v>
+        <v>-0.5158</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7922</v>
+        <v>-1.9918</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1893</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1805</v>
+        <v>-2.9733</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9911</v>
+        <v>2.5769</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1629</v>
+        <v>-0.8911</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0573</v>
+        <v>-0.1036</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1056</v>
+        <v>-0.7875</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1962</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>A. GARCIA TEJON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9799</v>
+        <v>-2.1041</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0905</v>
+        <v>-1.4874</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0705</v>
+        <v>-0.6168</v>
       </c>
       <c r="G22" t="n">
-        <v>0.973</v>
+        <v>-1.5122</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1211</v>
+        <v>-1.4031</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.148</v>
+        <v>-0.1091</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4807</v>
+        <v>0.1451</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6369</v>
+        <v>-0.5379</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8437</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5076</v>
+        <v>-1.6574</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5158</v>
+        <v>-0.8652</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9918</v>
+        <v>-0.7922</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3964</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9733</v>
+        <v>-2.1805</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5769</v>
+        <v>0.9911</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.616</v>
+        <v>0.5974</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6129</v>
+        <v>0.548</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.003</v>
+        <v>0.0495</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1962</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5993</v>
+        <v>-2.7293</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6814</v>
+        <v>-1.7833</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9179</v>
+        <v>-0.946</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0585</v>
@@ -2248,13 +2248,13 @@
         <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>0.587</v>
+        <v>0.457</v>
       </c>
       <c r="T23" t="n">
-        <v>0.503</v>
+        <v>0.4011</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0559</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5331</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.9184</v>
+        <v>-7.0203</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9932</v>
+        <v>-4.0951</v>
       </c>
       <c r="F24" t="n">
         <v>-2.9252</v>
@@ -2326,10 +2326,10 @@
         <v>0.5947</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0221</v>
+        <v>-0.1239</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2423</v>
+        <v>0.1405</v>
       </c>
       <c r="U24" t="n">
         <v>-0.2644</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.882700000000002</v>
+        <v>6.240900000000001</v>
       </c>
       <c r="E25" t="n">
         <v>15.1764</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.2939</v>
+        <v>-8.935699999999999</v>
       </c>
       <c r="G25" t="n">
         <v>2.810900000000001</v>
@@ -2389,7 +2389,7 @@
         <v>-16.7982</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.2083</v>
+        <v>-4.208299999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-12.59</v>
@@ -2404,16 +2404,16 @@
         <v>18.8312</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.497000000000001</v>
+        <v>-3.1388</v>
       </c>
       <c r="T25" t="n">
         <v>1.5427</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.039800000000001</v>
+        <v>-4.6813</v>
       </c>
       <c r="V25" t="n">
-        <v>6.568700000000001</v>
+        <v>6.568699999999999</v>
       </c>
       <c r="W25" t="n">
         <v>12.8558</v>
